--- a/data/Arisdorf/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/aggregated_investment_decision.xlsx
@@ -445,42 +445,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,28 +499,28 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012635090781166</v>
+        <v>35.45323738615242</v>
       </c>
       <c r="D2" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="E2" t="n">
-        <v>6.027760775346405</v>
+        <v>35.49238068312465</v>
       </c>
       <c r="F2" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="G2" t="n">
-        <v>6.027760775346406</v>
+        <v>35.45323738615242</v>
       </c>
       <c r="H2" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="I2" t="n">
-        <v>6.141230981562329</v>
+        <v>35.49886229078115</v>
       </c>
       <c r="J2" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="K2" t="n">
         <v>0.003</v>
@@ -536,28 +536,28 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>594.9639508018255</v>
+        <v>1361.546544670968</v>
       </c>
       <c r="D3" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="E3" t="n">
-        <v>594.9639508018258</v>
+        <v>1184.705019568216</v>
       </c>
       <c r="F3" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="G3" t="n">
-        <v>595.5396712652223</v>
+        <v>1330.564044832299</v>
       </c>
       <c r="H3" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="I3" t="n">
-        <v>595.5391177803915</v>
+        <v>1218.622880945311</v>
       </c>
       <c r="J3" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="K3" t="n">
         <v>0.003</v>
@@ -573,28 +573,28 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>1769.209872184993</v>
+        <v>1849.908965783201</v>
       </c>
       <c r="D4" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="E4" t="n">
-        <v>1787.813600308597</v>
+        <v>1910.726273769749</v>
       </c>
       <c r="F4" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="G4" t="n">
-        <v>1770.600959162138</v>
+        <v>2035.680003316621</v>
       </c>
       <c r="H4" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="I4" t="n">
-        <v>1767.470559045316</v>
+        <v>1735.523033213859</v>
       </c>
       <c r="J4" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="K4" t="n">
         <v>0.003</v>
@@ -610,28 +610,28 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>2186.016940706683</v>
+        <v>2132.530361235678</v>
       </c>
       <c r="D5" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="E5" t="n">
-        <v>2237.274552768718</v>
+        <v>2394.767340390908</v>
       </c>
       <c r="F5" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="G5" t="n">
-        <v>2171.391197017018</v>
+        <v>2376.803523835198</v>
       </c>
       <c r="H5" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="I5" t="n">
-        <v>2243.626840433342</v>
+        <v>2128.090080444596</v>
       </c>
       <c r="J5" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="K5" t="n">
         <v>0.003</v>
@@ -647,28 +647,28 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>2186.016940706683</v>
+        <v>2132.530361235678</v>
       </c>
       <c r="D6" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="E6" t="n">
-        <v>2238.60950732486</v>
+        <v>2394.767340390908</v>
       </c>
       <c r="F6" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="G6" t="n">
-        <v>2171.391197017018</v>
+        <v>2376.803523835198</v>
       </c>
       <c r="H6" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="I6" t="n">
-        <v>2244.961794989484</v>
+        <v>2128.090080444596</v>
       </c>
       <c r="J6" t="n">
-        <v>471337.0606824432</v>
+        <v>471610.0080283146</v>
       </c>
       <c r="K6" t="n">
         <v>0.003</v>
@@ -687,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>707.0055910236647</v>
+        <v>356.9692542338708</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>707.0055910236647</v>
+        <v>707.415012042472</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>356.7829589523546</v>
+        <v>707.415012042472</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>356.7829589523546</v>
+        <v>356.9692542338708</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -724,25 +724,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>707.0055910236647</v>
+        <v>495.0646755382476</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>707.0055910236647</v>
+        <v>707.415012042472</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>494.7904561143828</v>
+        <v>707.415012042472</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>494.7904561143828</v>
+        <v>495.0646755382476</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -761,25 +761,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>707.0055910236647</v>
+        <v>564.567146093171</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>707.0055910236647</v>
+        <v>707.415012042472</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>564.2486750564943</v>
+        <v>707.415012042472</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>564.2486750564943</v>
+        <v>564.567146093171</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -798,25 +798,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>707.0055910236647</v>
+        <v>603.9188263414687</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>707.0055910236647</v>
+        <v>707.415012042472</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>603.5753004354622</v>
+        <v>707.415012042472</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>603.5753004354622</v>
+        <v>603.9188263414687</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -835,25 +835,25 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>707.0055910236647</v>
+        <v>628.2066874383746</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>707.0055910236647</v>
+        <v>707.415012042472</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>627.8476976644408</v>
+        <v>707.415012042472</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>627.8476976644408</v>
+        <v>628.2066874383746</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -872,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11.99397521250205</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.607837863137207</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.607837863137207</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11.99397521250205</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.722747024218983</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>5.722747024218983</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>11.99397521250205</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.063248398539037</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.063248398539037</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -983,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.99397521250205</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7.964919593117228</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7.964919593117228</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1020,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11.99397521250205</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8.600938502920275</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8.600938502920275</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3126818435799518</v>
+        <v>0.3206425406068641</v>
       </c>
       <c r="D17" t="n">
-        <v>11.99397521250205</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3126818435799519</v>
+        <v>0.3204287281793758</v>
       </c>
       <c r="F17" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3127014969537156</v>
+        <v>0.3204286070995755</v>
       </c>
       <c r="H17" t="n">
-        <v>3.607837863137207</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3127015087558676</v>
+        <v>0.3206426616866648</v>
       </c>
       <c r="J17" t="n">
-        <v>3.607837863137207</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3126818435799518</v>
+        <v>0.3246214984107142</v>
       </c>
       <c r="D18" t="n">
-        <v>11.99397521250205</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3126818435799519</v>
+        <v>0.3244215211542166</v>
       </c>
       <c r="F18" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3127014969537156</v>
+        <v>0.3244215211542167</v>
       </c>
       <c r="H18" t="n">
-        <v>5.722747024218983</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3127015087558676</v>
+        <v>0.3246214289106438</v>
       </c>
       <c r="J18" t="n">
-        <v>5.722747024218983</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3217323713003519</v>
+        <v>0.3302983487864076</v>
       </c>
       <c r="D19" t="n">
-        <v>11.99397521250205</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="E19" t="n">
-        <v>0.321732371300352</v>
+        <v>0.3302945112335815</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3217323713003521</v>
+        <v>0.3302945112335815</v>
       </c>
       <c r="H19" t="n">
-        <v>7.063248398539037</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3217323713003519</v>
+        <v>0.3302982927400738</v>
       </c>
       <c r="J19" t="n">
-        <v>7.063248398539037</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3302514618736146</v>
+        <v>0.3337912312656334</v>
       </c>
       <c r="D20" t="n">
-        <v>11.99397521250205</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3302514906135794</v>
+        <v>0.3337829973890428</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3302541766555159</v>
+        <v>0.3337829973890428</v>
       </c>
       <c r="H20" t="n">
-        <v>7.964919593117228</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3302541766555159</v>
+        <v>0.3337911110122802</v>
       </c>
       <c r="J20" t="n">
-        <v>7.964919593117228</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3302514618736146</v>
+        <v>0.338141695074942</v>
       </c>
       <c r="D21" t="n">
-        <v>11.99397521250205</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3302514906135794</v>
+        <v>0.3376544610289568</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99397521250205</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3302541766555159</v>
+        <v>0.33778894053319</v>
       </c>
       <c r="H21" t="n">
-        <v>8.600938502920275</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3302541766555159</v>
+        <v>0.3381415874228698</v>
       </c>
       <c r="J21" t="n">
-        <v>8.600938502920275</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.1155074168940402</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.1153311411952941</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.1153311411952941</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.1155074168940402</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.11555538312</v>
+        <v>0.1200912455519105</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.11555538312</v>
+        <v>0.1198775477976471</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11555538312</v>
+        <v>0.1198775477976471</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.11555538312</v>
+        <v>0.1200906990137626</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.1246352230625761</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.1245978010070588</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.1245978010070588</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.1246346765244283</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1348269860987721</v>
+        <v>0.13511800378669</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1348272663577291</v>
+        <v>0.1348546850200699</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.1348546850200699</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.1349626750479327</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1348269860987721</v>
+        <v>0.1360233954614696</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1348272663577291</v>
+        <v>0.1348546850200699</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.1351580698570376</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.1360228489233218</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.0147365431046726</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0147365431046726</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.0275334314020259</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0275334314020259</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.03882132685350974</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03882132685350974</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.04888731824920112</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.04888731824920112</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.0579683588432312</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0579683588432312</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01310655965273057</v>
+        <v>0.0134704772311037</v>
       </c>
       <c r="D32" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01310655965273057</v>
+        <v>0.01346070294870424</v>
       </c>
       <c r="F32" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01310745809267406</v>
+        <v>0.01346069741362755</v>
       </c>
       <c r="H32" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01310745863220101</v>
+        <v>0.0134704827661803</v>
       </c>
       <c r="J32" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1646,28 +1646,28 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01319646235229359</v>
+        <v>0.01365237244499399</v>
       </c>
       <c r="D33" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0131964623522936</v>
+        <v>0.0136432306275541</v>
       </c>
       <c r="F33" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01319736079223708</v>
+        <v>0.01364323062755389</v>
       </c>
       <c r="H33" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01319736133176403</v>
+        <v>0.01365236926784792</v>
       </c>
       <c r="J33" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="K33" t="n">
         <v>175</v>
@@ -1683,28 +1683,28 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.013520298062806</v>
+        <v>0.01391188560502569</v>
       </c>
       <c r="D34" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01352029806280601</v>
+        <v>0.01391171017403935</v>
       </c>
       <c r="F34" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01352029806280601</v>
+        <v>0.01391171017403935</v>
       </c>
       <c r="H34" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="I34" t="n">
-        <v>0.013520298062806</v>
+        <v>0.01391188304290757</v>
       </c>
       <c r="J34" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="K34" t="n">
         <v>175</v>
@@ -1720,28 +1720,28 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01572038713692553</v>
+        <v>0.01562508743624304</v>
       </c>
       <c r="D35" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01572044988228875</v>
+        <v>0.01556527669537402</v>
       </c>
       <c r="F35" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01572631407450414</v>
+        <v>0.01556527669537402</v>
       </c>
       <c r="H35" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01572631407450415</v>
+        <v>0.01558958922182325</v>
       </c>
       <c r="J35" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="K35" t="n">
         <v>175</v>
@@ -1757,28 +1757,28 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01572038713692553</v>
+        <v>0.0156331557591957</v>
       </c>
       <c r="D36" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01572044988228874</v>
+        <v>0.01556527669537402</v>
       </c>
       <c r="F36" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01572631407450414</v>
+        <v>0.01556527669537402</v>
       </c>
       <c r="H36" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01572631407450415</v>
+        <v>0.01563303575742807</v>
       </c>
       <c r="J36" t="n">
-        <v>8.080063897413311</v>
+        <v>8.084742994771108</v>
       </c>
       <c r="K36" t="n">
         <v>175</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.135883270089286</v>
+        <v>0.03553253809114845</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.03553253809114845</v>
+        <v>1.135883270089286</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1.135883270089286</v>
+        <v>0.06628992744512983</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06628992744512983</v>
+        <v>1.135883270089286</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.135883270089286</v>
+        <v>0.09334953007617701</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09334953007617701</v>
+        <v>1.135883270089286</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.135883270089286</v>
+        <v>0.1174813095612829</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1174813095612829</v>
+        <v>1.135883270089286</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.135883270089286</v>
+        <v>0.1392411358567997</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1392411358567997</v>
+        <v>1.135883270089286</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>2.189654496557659</v>
+        <v>0.06849645897088857</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.06849645897088857</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.189654496557659</v>
+        <v>0.127787811942419</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.127787811942419</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2.189654496557659</v>
+        <v>0.1799509013516665</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1799509013516665</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2.189654496557659</v>
+        <v>0.2264699943350033</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2264699943350033</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>2.189654496557659</v>
+        <v>0.2684166474347946</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2684166474347946</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.0009475343490972921</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0009475343490972921</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.001767731398536796</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001767731398536796</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.002489320802031387</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.002489320802031387</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.003132834921634212</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.003132834921634212</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.003713096956181325</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.003713096956181325</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2719,25 +2719,25 @@
         <v>46023</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4285249050239265</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="D62" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4283831017311274</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="F62" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4283831017311274</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="H62" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4273193185478531</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="J62" t="n">
         <v>4.470300525600001</v>
@@ -2756,25 +2756,25 @@
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8371698919142299</v>
+        <v>0.4750877361504614</v>
       </c>
       <c r="D63" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8370280886214299</v>
+        <v>0.6589062827811409</v>
       </c>
       <c r="F63" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8350222907167945</v>
+        <v>0.6579357244426037</v>
       </c>
       <c r="H63" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8340471982784728</v>
+        <v>0.4915040778473956</v>
       </c>
       <c r="J63" t="n">
         <v>4.470300525600001</v>
@@ -2793,25 +2793,25 @@
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8371698919142299</v>
+        <v>0.4750877361504614</v>
       </c>
       <c r="D64" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8370280886214299</v>
+        <v>0.6619054793819794</v>
       </c>
       <c r="F64" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8350222907167945</v>
+        <v>0.6609349210434423</v>
       </c>
       <c r="H64" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8340471982784728</v>
+        <v>0.4915040778473956</v>
       </c>
       <c r="J64" t="n">
         <v>4.470300525600001</v>
@@ -2830,25 +2830,25 @@
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5026758658272612</v>
+        <v>0.5273170196457403</v>
       </c>
       <c r="D65" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5026460883130781</v>
+        <v>0.7146313707910997</v>
       </c>
       <c r="F65" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="G65" t="n">
-        <v>0.499863076821796</v>
+        <v>0.7136608124525626</v>
       </c>
       <c r="H65" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.499863076821796</v>
+        <v>0.5437355155235537</v>
       </c>
       <c r="J65" t="n">
         <v>4.470300525600001</v>
@@ -2867,25 +2867,25 @@
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4546290519369589</v>
+        <v>0.3472772489322486</v>
       </c>
       <c r="D66" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4545992744227765</v>
+        <v>0.4709724444469278</v>
       </c>
       <c r="F66" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.45382206083613</v>
+        <v>0.4387378055191104</v>
       </c>
       <c r="H66" t="n">
         <v>4.470300525600001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4537333700911773</v>
+        <v>0.3472794031131279</v>
       </c>
       <c r="J66" t="n">
         <v>4.470300525600001</v>
@@ -3015,25 +3015,25 @@
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="D70" t="n">
         <v>70.382286072</v>
       </c>
       <c r="E70" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="F70" t="n">
         <v>70.382286072</v>
       </c>
       <c r="G70" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="H70" t="n">
         <v>70.382286072</v>
       </c>
       <c r="I70" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="J70" t="n">
         <v>70.382286072</v>
@@ -3052,25 +3052,25 @@
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="D71" t="n">
         <v>70.382286072</v>
       </c>
       <c r="E71" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="F71" t="n">
         <v>70.382286072</v>
       </c>
       <c r="G71" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="H71" t="n">
         <v>70.382286072</v>
       </c>
       <c r="I71" t="n">
-        <v>2.156978033315449</v>
+        <v>3.881016711957625</v>
       </c>
       <c r="J71" t="n">
         <v>70.382286072</v>
@@ -3496,7 +3496,7 @@
         <v>47849</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.0008750366264110481</v>
       </c>
       <c r="D83" t="n">
         <v>4.470300525600001</v>
@@ -3514,7 +3514,7 @@
         <v>4.470300525600001</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>0.0009043037442274315</v>
       </c>
       <c r="J83" t="n">
         <v>4.470300525600001</v>
@@ -3533,7 +3533,7 @@
         <v>49675</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.002144261466413958</v>
       </c>
       <c r="D84" t="n">
         <v>4.470300525600001</v>
@@ -3551,7 +3551,7 @@
         <v>4.470300525600001</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>0.002175764081691177</v>
       </c>
       <c r="J84" t="n">
         <v>4.470300525600001</v>
@@ -3570,7 +3570,7 @@
         <v>51502</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.004370841141090771</v>
       </c>
       <c r="D85" t="n">
         <v>4.470300525600001</v>
@@ -3588,7 +3588,7 @@
         <v>4.470300525600001</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>0.004397954078027916</v>
       </c>
       <c r="J85" t="n">
         <v>4.470300525600001</v>
@@ -3607,7 +3607,7 @@
         <v>53328</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.003495804514679738</v>
       </c>
       <c r="D86" t="n">
         <v>4.470300525600001</v>
@@ -3625,7 +3625,7 @@
         <v>4.470300525600001</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>0.003493650333800474</v>
       </c>
       <c r="J86" t="n">
         <v>4.470300525600001</v>
@@ -4572,19 +4572,19 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>19.24846222160268</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>19.24846222160268</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -4606,22 +4606,22 @@
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>0.9518352754008268</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>19.24846222160268</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9518352754008268</v>
+        <v>17.33655820369192</v>
       </c>
       <c r="F113" t="n">
-        <v>19.24846222160268</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>17.38027421848903</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4643,22 +4643,22 @@
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>2.457302264702742</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>19.24846222160268</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>2.462129022715707</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="F114" t="n">
-        <v>19.24846222160268</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -4680,22 +4680,22 @@
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>9.490291696759236</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>19.24846222160268</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>9.490289205800252</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="F115" t="n">
-        <v>19.24846222160268</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -4717,22 +4717,22 @@
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>9.694411338198092</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>19.24846222160268</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>9.694408793662921</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="F116" t="n">
-        <v>19.24846222160268</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>265.5568819273586</v>
+        <v>146.14775294066</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>146.14775294066</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>265.5568819273586</v>
+        <v>195.9362286536411</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>195.9362286536411</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>265.5568819273586</v>
+        <v>220.0614813359284</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>220.0614813359284</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>265.5568819273586</v>
+        <v>233.3262203850576</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>233.3262203850576</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>265.5568819273586</v>
+        <v>241.3250919862749</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>241.3250919862749</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>12.89437269088045</v>
+        <v>6.98212132639982</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>6.98212132639982</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>12.89437269088045</v>
+        <v>9.447276092768421</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>9.447276092768421</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>12.89437269088045</v>
+        <v>10.64177905330155</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>10.64177905330155</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>12.89437269088045</v>
+        <v>11.29855020813871</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>11.29855020813871</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -5087,10 +5087,10 @@
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>11.82267528667671</v>
       </c>
       <c r="D126" t="n">
-        <v>12.89437269088045</v>
+        <v>11.69459479819572</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>11.69459479819572</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5312,25 +5312,25 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2121776417932228</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2121776417932293</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K132" t="n">
         <v>0.017</v>
@@ -5349,25 +5349,25 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E133" t="n">
-        <v>0.2121776417932228</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2121776417932293</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K133" t="n">
         <v>0.017</v>
@@ -5386,25 +5386,25 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2941538065981567</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I134" t="n">
-        <v>0.294153806598164</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K134" t="n">
         <v>0.017</v>
@@ -5423,25 +5423,25 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E135" t="n">
-        <v>0.08197616480493385</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I135" t="n">
-        <v>0.08197616480493471</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K135" t="n">
         <v>0.017</v>
@@ -5460,25 +5460,25 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E136" t="n">
-        <v>0.08197616480493385</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I136" t="n">
-        <v>0.08197616480493471</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K136" t="n">
         <v>0.017</v>
@@ -5497,25 +5497,25 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K137" t="n">
         <v>0.08</v>
@@ -5531,28 +5531,28 @@
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2261354984775276</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2365368956604268</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G138" t="n">
-        <v>0.227125543405866</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2360739630188868</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K138" t="n">
         <v>0.08</v>
@@ -5568,28 +5568,28 @@
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3802797699120731</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4825616337922584</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3787847055919699</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4562807230230681</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K139" t="n">
         <v>0.08</v>
@@ -5605,28 +5605,28 @@
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3802797699120731</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4825616337922584</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3787847055919699</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4562807230230681</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K140" t="n">
         <v>0.08</v>
@@ -5642,28 +5642,28 @@
         <v>53328</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1541442714345456</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2460247381318316</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1516591621861038</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2202067600041814</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K141" t="n">
         <v>0.08</v>
@@ -5679,28 +5679,28 @@
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>31.06383992251658</v>
       </c>
       <c r="D142" t="n">
-        <v>552.4317025740247</v>
+        <v>187.674165119542</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>24.62918363103576</v>
       </c>
       <c r="F142" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>36.27727923968874</v>
       </c>
       <c r="H142" t="n">
-        <v>146.7056153048075</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>20.29473480258355</v>
       </c>
       <c r="J142" t="n">
-        <v>146.7056153048075</v>
+        <v>187.674165119542</v>
       </c>
       <c r="K142" t="n">
         <v>0.017</v>
@@ -5716,28 +5716,28 @@
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>56.22240699194667</v>
       </c>
       <c r="D143" t="n">
-        <v>552.4317025740247</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>52.86819216892452</v>
       </c>
       <c r="F143" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>61.2989596318371</v>
       </c>
       <c r="H143" t="n">
-        <v>218.6411790307994</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>48.53374334047231</v>
       </c>
       <c r="J143" t="n">
-        <v>218.6411790307994</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="K143" t="n">
         <v>0.017</v>
@@ -5753,28 +5753,28 @@
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>83.11847781917876</v>
+        <v>107.9533645180444</v>
       </c>
       <c r="D144" t="n">
-        <v>552.4317025740247</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="E144" t="n">
-        <v>88.25146084026098</v>
+        <v>105.7329678515848</v>
       </c>
       <c r="F144" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G144" t="n">
-        <v>83.03387907435497</v>
+        <v>111.5468086003072</v>
       </c>
       <c r="H144" t="n">
-        <v>266.8200082731564</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I144" t="n">
-        <v>88.40188282604353</v>
+        <v>102.3356183429869</v>
       </c>
       <c r="J144" t="n">
-        <v>266.8200082731564</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="K144" t="n">
         <v>0.017</v>
@@ -5790,28 +5790,28 @@
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>137.4965700659751</v>
+        <v>121.6040887499884</v>
       </c>
       <c r="D145" t="n">
-        <v>552.4317025740247</v>
+        <v>382.129751166617</v>
       </c>
       <c r="E145" t="n">
-        <v>135.0827088855116</v>
+        <v>126.21491902212</v>
       </c>
       <c r="F145" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G145" t="n">
-        <v>137.3489528492098</v>
+        <v>121.7274815775719</v>
       </c>
       <c r="H145" t="n">
-        <v>300.7886739307696</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I145" t="n">
-        <v>135.0831563012655</v>
+        <v>124.6799277277981</v>
       </c>
       <c r="J145" t="n">
-        <v>300.7886739307696</v>
+        <v>382.129751166617</v>
       </c>
       <c r="K145" t="n">
         <v>0.017</v>
@@ -5827,28 +5827,28 @@
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>137.4965700659751</v>
+        <v>121.6040887499884</v>
       </c>
       <c r="D146" t="n">
-        <v>552.4317025740247</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="E146" t="n">
-        <v>135.0827088855116</v>
+        <v>126.21491902212</v>
       </c>
       <c r="F146" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G146" t="n">
-        <v>137.3489528492098</v>
+        <v>121.7274815775719</v>
       </c>
       <c r="H146" t="n">
-        <v>325.7388167399461</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I146" t="n">
-        <v>135.0831563012655</v>
+        <v>124.6799277277981</v>
       </c>
       <c r="J146" t="n">
-        <v>325.7388167399461</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="K146" t="n">
         <v>0.017</v>
@@ -5864,28 +5864,28 @@
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>0.002004806806213684</v>
+        <v>1.28098332541133</v>
       </c>
       <c r="D147" t="n">
-        <v>24.58434289929532</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="E147" t="n">
-        <v>0.05013133668662601</v>
+        <v>1.304342804576988</v>
       </c>
       <c r="F147" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G147" t="n">
-        <v>0.02505216113119287</v>
+        <v>1.280983325411331</v>
       </c>
       <c r="H147" t="n">
-        <v>6.134106096981654</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I147" t="n">
-        <v>0.050131336686626</v>
+        <v>1.303259487680379</v>
       </c>
       <c r="J147" t="n">
-        <v>6.134106096981654</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="K147" t="n">
         <v>0.08</v>
@@ -5901,28 +5901,28 @@
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>2.474082408075044</v>
+        <v>4.795667130189207</v>
       </c>
       <c r="D148" t="n">
-        <v>24.58434289929532</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="E148" t="n">
-        <v>2.733923597836659</v>
+        <v>4.814147516672517</v>
       </c>
       <c r="F148" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G148" t="n">
-        <v>2.411924539313729</v>
+        <v>4.814133475918659</v>
       </c>
       <c r="H148" t="n">
-        <v>9.405348018312193</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I148" t="n">
-        <v>2.733969817043408</v>
+        <v>4.810659007768463</v>
       </c>
       <c r="J148" t="n">
-        <v>9.405348018312193</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="K148" t="n">
         <v>0.08</v>
@@ -5938,28 +5938,28 @@
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>5.557041341382664</v>
+        <v>6.148476580181235</v>
       </c>
       <c r="D149" t="n">
-        <v>24.58434289929532</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="E149" t="n">
-        <v>5.801171567977478</v>
+        <v>6.326539067003607</v>
       </c>
       <c r="F149" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G149" t="n">
-        <v>5.49705434242902</v>
+        <v>6.2044450282026</v>
       </c>
       <c r="H149" t="n">
-        <v>11.5962616328708</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I149" t="n">
-        <v>5.82001020125486</v>
+        <v>6.291179300561396</v>
       </c>
       <c r="J149" t="n">
-        <v>11.5962616328708</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="K149" t="n">
         <v>0.08</v>
@@ -5975,28 +5975,28 @@
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>5.95676295216092</v>
+        <v>6.036269922327352</v>
       </c>
       <c r="D150" t="n">
-        <v>24.58434289929532</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="E150" t="n">
-        <v>6.172197610429165</v>
+        <v>6.119546799796065</v>
       </c>
       <c r="F150" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G150" t="n">
-        <v>5.867264943458535</v>
+        <v>6.082396691514937</v>
       </c>
       <c r="H150" t="n">
-        <v>13.14097355775553</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I150" t="n">
-        <v>6.176309168442729</v>
+        <v>6.045522070291846</v>
       </c>
       <c r="J150" t="n">
-        <v>13.14097355775553</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="K150" t="n">
         <v>0.08</v>
@@ -6012,28 +6012,28 @@
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>6.21667488103452</v>
+        <v>6.0370483974192</v>
       </c>
       <c r="D151" t="n">
-        <v>24.58434289929532</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="E151" t="n">
-        <v>6.160618490564987</v>
+        <v>6.125708789907637</v>
       </c>
       <c r="F151" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G151" t="n">
-        <v>6.221876905855162</v>
+        <v>6.087908586621852</v>
       </c>
       <c r="H151" t="n">
-        <v>14.27557164628169</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I151" t="n">
-        <v>6.15589320965017</v>
+        <v>6.050717096170695</v>
       </c>
       <c r="J151" t="n">
-        <v>14.27557164628169</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="K151" t="n">
         <v>0.08</v>
@@ -6052,25 +6052,25 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>552.4317025740247</v>
+        <v>187.674165119542</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>146.7056153048075</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>146.7056153048075</v>
+        <v>187.674165119542</v>
       </c>
       <c r="K152" t="n">
         <v>0.017</v>
@@ -6089,25 +6089,25 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>552.4317025740247</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>218.6411790307994</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>218.6411790307994</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="K153" t="n">
         <v>0.017</v>
@@ -6126,25 +6126,25 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>552.4317025740247</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>266.8200082731564</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>266.8200082731564</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="K154" t="n">
         <v>0.017</v>
@@ -6163,25 +6163,25 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>552.4317025740247</v>
+        <v>382.129751166617</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>300.7886739307696</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>300.7886739307696</v>
+        <v>382.129751166617</v>
       </c>
       <c r="K155" t="n">
         <v>0.017</v>
@@ -6200,25 +6200,25 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>552.4317025740247</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>325.7388167399461</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>325.7388167399461</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="K156" t="n">
         <v>0.017</v>
@@ -6237,25 +6237,25 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>24.58434289929532</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>6.134106096981654</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>6.134106096981654</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="K157" t="n">
         <v>0.08</v>
@@ -6274,25 +6274,25 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>24.58434289929532</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>9.405348018312193</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>9.405348018312193</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="K158" t="n">
         <v>0.08</v>
@@ -6311,25 +6311,25 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>24.58434289929532</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>11.5962616328708</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>11.5962616328708</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="K159" t="n">
         <v>0.08</v>
@@ -6348,25 +6348,25 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>24.58434289929532</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>13.14097355775553</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>13.14097355775553</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="K160" t="n">
         <v>0.08</v>
@@ -6385,25 +6385,25 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>24.58434289929532</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>14.27557164628169</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>14.27557164628169</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="K161" t="n">
         <v>0.08</v>
@@ -6419,28 +6419,28 @@
         <v>46023</v>
       </c>
       <c r="C162" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E162" t="n">
-        <v>47.8543316979744</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G162" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I162" t="n">
-        <v>47.85433169797439</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K162" t="n">
         <v>0.017</v>
@@ -6456,28 +6456,28 @@
         <v>47849</v>
       </c>
       <c r="C163" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E163" t="n">
-        <v>47.8543316979744</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G163" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I163" t="n">
-        <v>47.85433169797439</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K163" t="n">
         <v>0.017</v>
@@ -6493,28 +6493,28 @@
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>71.75129840733824</v>
+        <v>76.05297945735737</v>
       </c>
       <c r="D164" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E164" t="n">
-        <v>74.3850047771255</v>
+        <v>70.09486655141411</v>
       </c>
       <c r="F164" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G164" t="n">
-        <v>71.71956197435875</v>
+        <v>73.24991226070851</v>
       </c>
       <c r="H164" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I164" t="n">
-        <v>74.69601385550129</v>
+        <v>73.42470297873918</v>
       </c>
       <c r="J164" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K164" t="n">
         <v>0.017</v>
@@ -6530,28 +6530,28 @@
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>73.48511640622684</v>
+        <v>90.52017707485672</v>
       </c>
       <c r="D165" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E165" t="n">
-        <v>74.66170808015798</v>
+        <v>79.7275369380185</v>
       </c>
       <c r="F165" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G165" t="n">
-        <v>73.95054330755171</v>
+        <v>84.6875929299607</v>
       </c>
       <c r="H165" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I165" t="n">
-        <v>74.63605658928228</v>
+        <v>87.54214883290159</v>
       </c>
       <c r="J165" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K165" t="n">
         <v>0.017</v>
@@ -6567,28 +6567,28 @@
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>73.48511640622684</v>
+        <v>90.52017707485672</v>
       </c>
       <c r="D166" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E166" t="n">
-        <v>74.71423671798919</v>
+        <v>79.7275369380185</v>
       </c>
       <c r="F166" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G166" t="n">
-        <v>73.9505433075517</v>
+        <v>84.6875929299607</v>
       </c>
       <c r="H166" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I166" t="n">
-        <v>74.68858522711346</v>
+        <v>87.54214883290157</v>
       </c>
       <c r="J166" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K166" t="n">
         <v>0.017</v>
@@ -6607,25 +6607,25 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K167" t="n">
         <v>0.08</v>
@@ -6641,28 +6641,28 @@
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>0.02977653854697437</v>
+        <v>0.08894748070658121</v>
       </c>
       <c r="D168" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E168" t="n">
-        <v>0.02977737867431045</v>
+        <v>0.09132442895142252</v>
       </c>
       <c r="F168" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G168" t="n">
-        <v>0.02751219859073391</v>
+        <v>0.092217225166217</v>
       </c>
       <c r="H168" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I168" t="n">
-        <v>0.02752624896539657</v>
+        <v>0.08726548408377678</v>
       </c>
       <c r="J168" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K168" t="n">
         <v>0.08</v>
@@ -6678,28 +6678,28 @@
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>2.967718325364301</v>
+        <v>2.33800578137556</v>
       </c>
       <c r="D169" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E169" t="n">
-        <v>2.956100977482098</v>
+        <v>2.234659444358468</v>
       </c>
       <c r="F169" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G169" t="n">
-        <v>2.965768224848834</v>
+        <v>2.341275525835196</v>
       </c>
       <c r="H169" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I169" t="n">
-        <v>2.960875411830202</v>
+        <v>2.193281115124412</v>
       </c>
       <c r="J169" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K169" t="n">
         <v>0.08</v>
@@ -6715,28 +6715,28 @@
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>3.446156620345086</v>
+        <v>3.450212439229441</v>
       </c>
       <c r="D170" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E170" t="n">
-        <v>3.414089625963657</v>
+        <v>3.44147348243352</v>
       </c>
       <c r="F170" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G170" t="n">
-        <v>3.430683773463028</v>
+        <v>3.462397539498288</v>
       </c>
       <c r="H170" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I170" t="n">
-        <v>3.411838496254744</v>
+        <v>3.440962750242947</v>
       </c>
       <c r="J170" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K170" t="n">
         <v>0.08</v>
@@ -6752,28 +6752,28 @@
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>3.846519619733094</v>
+        <v>3.456285337016892</v>
       </c>
       <c r="D171" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E171" t="n">
-        <v>3.908230379620092</v>
+        <v>3.441973743150347</v>
       </c>
       <c r="F171" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G171" t="n">
-        <v>3.821442015738854</v>
+        <v>3.463547895219771</v>
       </c>
       <c r="H171" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I171" t="n">
-        <v>3.888535178070369</v>
+        <v>3.442618722945707</v>
       </c>
       <c r="J171" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K171" t="n">
         <v>0.08</v>
@@ -6792,25 +6792,25 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K172" t="n">
         <v>0.017</v>
@@ -6829,25 +6829,25 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K173" t="n">
         <v>0.017</v>
@@ -6866,25 +6866,25 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K174" t="n">
         <v>0.017</v>
@@ -6903,25 +6903,25 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K175" t="n">
         <v>0.017</v>
@@ -6940,25 +6940,25 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K176" t="n">
         <v>0.017</v>
@@ -6977,25 +6977,25 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K177" t="n">
         <v>0.08</v>
@@ -7014,25 +7014,25 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K178" t="n">
         <v>0.08</v>
@@ -7051,25 +7051,25 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K179" t="n">
         <v>0.08</v>
@@ -7088,25 +7088,25 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K180" t="n">
         <v>0.08</v>
@@ -7125,25 +7125,25 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K181" t="n">
         <v>0.08</v>
@@ -7162,25 +7162,25 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>552.4317025740247</v>
+        <v>83.42697229498918</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>64.10204165540358</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>64.10204165540358</v>
+        <v>83.42697229498918</v>
       </c>
       <c r="K182" t="n">
         <v>0.017</v>
@@ -7199,25 +7199,25 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>552.4317025740247</v>
+        <v>114.9301450330319</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>89.06458097131986</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>89.06458097131986</v>
+        <v>114.9301450330319</v>
       </c>
       <c r="K183" t="n">
         <v>0.017</v>
@@ -7236,25 +7236,25 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>552.4317025740247</v>
+        <v>140.5979460799421</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>109.4032782230057</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>109.4032782230057</v>
+        <v>140.5979460799421</v>
       </c>
       <c r="K184" t="n">
         <v>0.017</v>
@@ -7273,25 +7273,25 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>552.4317025740247</v>
+        <v>162.1111102622133</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>126.4499170226973</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>126.4499170226973</v>
+        <v>162.1111102622133</v>
       </c>
       <c r="K185" t="n">
         <v>0.017</v>
@@ -7310,25 +7310,25 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>552.4317025740247</v>
+        <v>180.494690804983</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>141.0167308443426</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>141.0167308443426</v>
+        <v>180.494690804983</v>
       </c>
       <c r="K186" t="n">
         <v>0.017</v>
@@ -7347,25 +7347,25 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>24.58434289929532</v>
+        <v>3.069304059722748</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>2.377740552910585</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>2.377740552910585</v>
+        <v>3.069304059722748</v>
       </c>
       <c r="K187" t="n">
         <v>0.08</v>
@@ -7384,25 +7384,25 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>24.58434289929532</v>
+        <v>4.498506149122878</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>3.512902367783275</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>3.512902367783275</v>
+        <v>4.498506149122878</v>
       </c>
       <c r="K188" t="n">
         <v>0.08</v>
@@ -7421,25 +7421,25 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>24.58434289929532</v>
+        <v>5.662975365972627</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>4.437796754214907</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>4.437796754214907</v>
+        <v>5.662975365972627</v>
       </c>
       <c r="K189" t="n">
         <v>0.08</v>
@@ -7458,25 +7458,25 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>24.58434289929532</v>
+        <v>6.638961481865675</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>5.21298605657082</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>5.21298605657082</v>
+        <v>6.638961481865675</v>
       </c>
       <c r="K190" t="n">
         <v>0.08</v>
@@ -7495,25 +7495,25 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>24.58434289929532</v>
+        <v>7.472968010060661</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>5.87540627774392</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>5.87540627774392</v>
+        <v>7.472968010060661</v>
       </c>
       <c r="K191" t="n">
         <v>0.08</v>
@@ -7529,28 +7529,28 @@
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>37.42670714758817</v>
+        <v>7.352217337365687</v>
       </c>
       <c r="D192" t="n">
-        <v>552.4317025740247</v>
+        <v>83.42697229498918</v>
       </c>
       <c r="E192" t="n">
-        <v>28.95748566899951</v>
+        <v>13.78687362884651</v>
       </c>
       <c r="F192" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G192" t="n">
-        <v>37.42670714758816</v>
+        <v>2.13877802019353</v>
       </c>
       <c r="H192" t="n">
-        <v>64.10204165540358</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I192" t="n">
-        <v>28.95748566899952</v>
+        <v>18.12132245729873</v>
       </c>
       <c r="J192" t="n">
-        <v>64.10204165540358</v>
+        <v>83.42697229498918</v>
       </c>
       <c r="K192" t="n">
         <v>0.017</v>
@@ -7566,28 +7566,28 @@
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>37.42670714758817</v>
+        <v>7.352217337365687</v>
       </c>
       <c r="D193" t="n">
-        <v>552.4317025740247</v>
+        <v>114.9301450330319</v>
       </c>
       <c r="E193" t="n">
-        <v>28.95748566899951</v>
+        <v>13.78687362884651</v>
       </c>
       <c r="F193" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G193" t="n">
-        <v>37.42670714758816</v>
+        <v>2.13877802019353</v>
       </c>
       <c r="H193" t="n">
-        <v>89.06458097131986</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I193" t="n">
-        <v>28.95748566899952</v>
+        <v>18.12132245729873</v>
       </c>
       <c r="J193" t="n">
-        <v>89.06458097131986</v>
+        <v>114.9301450330319</v>
       </c>
       <c r="K193" t="n">
         <v>0.017</v>
@@ -7603,28 +7603,28 @@
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>37.42870522213487</v>
+        <v>7.352217337365687</v>
       </c>
       <c r="D194" t="n">
-        <v>552.4317025740247</v>
+        <v>140.5979460799421</v>
       </c>
       <c r="E194" t="n">
-        <v>28.95748566899952</v>
+        <v>13.78687362884651</v>
       </c>
       <c r="F194" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G194" t="n">
-        <v>37.52705437389957</v>
+        <v>2.13877802019353</v>
       </c>
       <c r="H194" t="n">
-        <v>109.4032782230057</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I194" t="n">
-        <v>28.95748566899952</v>
+        <v>18.12132245729873</v>
       </c>
       <c r="J194" t="n">
-        <v>109.4032782230057</v>
+        <v>140.5979460799421</v>
       </c>
       <c r="K194" t="n">
         <v>0.017</v>
@@ -7640,28 +7640,28 @@
         <v>51502</v>
       </c>
       <c r="C195" t="n">
-        <v>0.001998074546704755</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>552.4317025740247</v>
+        <v>162.1111102622133</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G195" t="n">
-        <v>0.1003472263114094</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>126.4499170226973</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>126.4499170226973</v>
+        <v>162.1111102622133</v>
       </c>
       <c r="K195" t="n">
         <v>0.017</v>
@@ -7677,28 +7677,28 @@
         <v>53328</v>
       </c>
       <c r="C196" t="n">
-        <v>0.001998074546704755</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>552.4317025740247</v>
+        <v>180.494690804983</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>552.4317025740247</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G196" t="n">
-        <v>0.1003472263114094</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>141.0167308443426</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>141.0167308443426</v>
+        <v>180.494690804983</v>
       </c>
       <c r="K196" t="n">
         <v>0.017</v>
@@ -7714,28 +7714,28 @@
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0650486978000249</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>24.58434289929532</v>
+        <v>3.069304059722748</v>
       </c>
       <c r="E197" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="F197" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G197" t="n">
-        <v>0.03919183118612408</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>2.377740552910585</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="J197" t="n">
-        <v>2.377740552910585</v>
+        <v>3.069304059722748</v>
       </c>
       <c r="K197" t="n">
         <v>0.08</v>
@@ -7751,28 +7751,28 @@
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0.3450438561495588</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>24.58434289929532</v>
+        <v>4.498506149122878</v>
       </c>
       <c r="E198" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="F198" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4057773302666071</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>3.512902367783275</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="J198" t="n">
-        <v>3.512902367783275</v>
+        <v>4.498506149122878</v>
       </c>
       <c r="K198" t="n">
         <v>0.08</v>
@@ -7788,28 +7788,28 @@
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3450438561495588</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>24.58434289929532</v>
+        <v>5.662975365972627</v>
       </c>
       <c r="E199" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="F199" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4057773302666071</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>4.437796754214907</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="J199" t="n">
-        <v>4.437796754214907</v>
+        <v>5.662975365972627</v>
       </c>
       <c r="K199" t="n">
         <v>0.08</v>
@@ -7825,28 +7825,28 @@
         <v>51502</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2799951583495339</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>24.58434289929532</v>
+        <v>6.638961481865675</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G200" t="n">
-        <v>0.366585499080483</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>5.21298605657082</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>5.21298605657082</v>
+        <v>6.638961481865675</v>
       </c>
       <c r="K200" t="n">
         <v>0.08</v>
@@ -7865,25 +7865,25 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>24.58434289929532</v>
+        <v>7.472968010060661</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>24.58434289929532</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>5.87540627774392</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>5.87540627774392</v>
+        <v>7.472968010060661</v>
       </c>
       <c r="K201" t="n">
         <v>0.08</v>
@@ -7902,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>4</v>
+        <v>1.084828228313528</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -7914,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1.084828228313528</v>
+        <v>4</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>1.748391275895091</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>1.748391275895091</v>
+        <v>4</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>2.182785755513471</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>2.182785755513471</v>
+        <v>4</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>2.483031451106882</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>2.483031451106882</v>
+        <v>4</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>2.699949766579019</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>2.699949766579019</v>
+        <v>4</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
+        <v>1.084828228313528</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1.084828228313528</v>
+        <v>4</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>4</v>
+        <v>1.748391275895091</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>1.748391275895091</v>
+        <v>4</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>4</v>
+        <v>2.182785755513471</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>2.182785755513471</v>
+        <v>4</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>4</v>
+        <v>2.483031451106882</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>2.483031451106882</v>
+        <v>4</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>4</v>
+        <v>2.699949766579019</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>2.699949766579019</v>
+        <v>4</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>4</v>
+        <v>1.084828228313528</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>1.084828228313528</v>
+        <v>4</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>4</v>
+        <v>1.748391275895091</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>1.748391275895091</v>
+        <v>4</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>4</v>
+        <v>2.182785755513471</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>2.182785755513471</v>
+        <v>4</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>2.483031451106882</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>2.483031451106882</v>
+        <v>4</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>4</v>
+        <v>2.699949766579019</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>2.699949766579019</v>
+        <v>4</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>

--- a/data/Arisdorf/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,42 +445,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,25 +499,25 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>35.45323738615242</v>
+        <v>332.2490948757745</v>
       </c>
       <c r="D2" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="E2" t="n">
-        <v>35.49238068312465</v>
+        <v>330.6094283722144</v>
       </c>
       <c r="F2" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="G2" t="n">
-        <v>35.45323738615242</v>
+        <v>332.2450970979023</v>
       </c>
       <c r="H2" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="I2" t="n">
-        <v>35.49886229078115</v>
+        <v>330.0728345173284</v>
       </c>
       <c r="J2" t="n">
         <v>471610.0080283146</v>
@@ -536,25 +536,25 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>1361.546544670968</v>
+        <v>849.1105133909766</v>
       </c>
       <c r="D3" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="E3" t="n">
-        <v>1184.705019568216</v>
+        <v>881.5614833405472</v>
       </c>
       <c r="F3" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="G3" t="n">
-        <v>1330.564044832299</v>
+        <v>881.4492898333076</v>
       </c>
       <c r="H3" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="I3" t="n">
-        <v>1218.622880945311</v>
+        <v>881.2196825681149</v>
       </c>
       <c r="J3" t="n">
         <v>471610.0080283146</v>
@@ -573,25 +573,25 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>1849.908965783201</v>
+        <v>1027.748470388632</v>
       </c>
       <c r="D4" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="E4" t="n">
-        <v>1910.726273769749</v>
+        <v>1214.739048841393</v>
       </c>
       <c r="F4" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="G4" t="n">
-        <v>2035.680003316621</v>
+        <v>1070.570926949039</v>
       </c>
       <c r="H4" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="I4" t="n">
-        <v>1735.523033213859</v>
+        <v>1211.045482585356</v>
       </c>
       <c r="J4" t="n">
         <v>471610.0080283146</v>
@@ -610,25 +610,25 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>2132.530361235678</v>
+        <v>1065.240971046333</v>
       </c>
       <c r="D5" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="E5" t="n">
-        <v>2394.767340390908</v>
+        <v>1269.248604741868</v>
       </c>
       <c r="F5" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="G5" t="n">
-        <v>2376.803523835198</v>
+        <v>1110.976930702383</v>
       </c>
       <c r="H5" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="I5" t="n">
-        <v>2128.090080444596</v>
+        <v>1262.452801955564</v>
       </c>
       <c r="J5" t="n">
         <v>471610.0080283146</v>
@@ -647,25 +647,25 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>2132.530361235678</v>
+        <v>1065.240971046333</v>
       </c>
       <c r="D6" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="E6" t="n">
-        <v>2394.767340390908</v>
+        <v>1269.248604741868</v>
       </c>
       <c r="F6" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="G6" t="n">
-        <v>2376.803523835198</v>
+        <v>1110.976930702382</v>
       </c>
       <c r="H6" t="n">
         <v>471610.0080283146</v>
       </c>
       <c r="I6" t="n">
-        <v>2128.090080444596</v>
+        <v>1262.452801955564</v>
       </c>
       <c r="J6" t="n">
         <v>471610.0080283146</v>
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -687,34 +687,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>356.9692542338708</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>707.415012042472</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>707.415012042472</v>
+        <v>1.610902838548527</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>356.9692542338708</v>
+        <v>1.610902838548527</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -724,34 +724,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>495.0646755382476</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>707.415012042472</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>707.415012042472</v>
+        <v>2.196544504272533</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>495.0646755382476</v>
+        <v>2.196544504272533</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -761,34 +761,34 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>564.567146093171</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>707.415012042472</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>707.415012042472</v>
+        <v>2.491293904674478</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>564.567146093171</v>
+        <v>2.491293904674478</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -798,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>603.9188263414687</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>707.415012042472</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>707.415012042472</v>
+        <v>2.658178391878842</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>603.9188263414687</v>
+        <v>2.658178391878842</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -835,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>628.2066874383746</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>707.415012042472</v>
+        <v>3.09708996488764</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>707.415012042472</v>
+        <v>2.761179514546871</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>628.2066874383746</v>
+        <v>2.761179514546871</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="12">
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4.500083374149693</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>14.96017573162526</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7.138025519738575</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>14.96017573162526</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>8.810042992928743</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>14.96017573162526</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>9.934704273616871</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>14.96017573162526</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>10.72801545616561</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14.96017573162526</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3206425406068641</v>
+        <v>0.3899959087758609</v>
       </c>
       <c r="D17" t="n">
-        <v>4.500083374149693</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3204287281793758</v>
+        <v>0.3899959087758609</v>
       </c>
       <c r="F17" t="n">
         <v>14.96017573162526</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3204286070995755</v>
+        <v>0.3925051518584075</v>
       </c>
       <c r="H17" t="n">
-        <v>14.96017573162526</v>
+        <v>4.500083374149693</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3206426616866648</v>
+        <v>0.3908464687352801</v>
       </c>
       <c r="J17" t="n">
         <v>4.500083374149693</v>
@@ -1091,25 +1091,25 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3246214984107142</v>
+        <v>0.4212607021620205</v>
       </c>
       <c r="D18" t="n">
-        <v>7.138025519738575</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3244215211542166</v>
+        <v>0.4210436558163798</v>
       </c>
       <c r="F18" t="n">
         <v>14.96017573162526</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3244215211542167</v>
+        <v>0.4240266375169042</v>
       </c>
       <c r="H18" t="n">
-        <v>14.96017573162526</v>
+        <v>7.138025519738575</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3246214289106438</v>
+        <v>0.421608834213296</v>
       </c>
       <c r="J18" t="n">
         <v>7.138025519738575</v>
@@ -1128,25 +1128,25 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3302983487864076</v>
+        <v>0.5147205725411766</v>
       </c>
       <c r="D19" t="n">
-        <v>8.810042992928743</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3302945112335815</v>
+        <v>0.5147205725411766</v>
       </c>
       <c r="F19" t="n">
         <v>14.96017573162526</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3302945112335815</v>
+        <v>0.5145464461757276</v>
       </c>
       <c r="H19" t="n">
-        <v>14.96017573162526</v>
+        <v>8.810042992928743</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3302982927400738</v>
+        <v>0.5145444990695518</v>
       </c>
       <c r="J19" t="n">
         <v>8.810042992928743</v>
@@ -1165,25 +1165,25 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3337912312656334</v>
+        <v>0.3332076091645323</v>
       </c>
       <c r="D20" t="n">
-        <v>9.934704273616871</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3337829973890428</v>
+        <v>0.3329704544190604</v>
       </c>
       <c r="F20" t="n">
         <v>14.96017573162526</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3337829973890428</v>
+        <v>0.5633225606227865</v>
       </c>
       <c r="H20" t="n">
-        <v>14.96017573162526</v>
+        <v>9.934704273616871</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3337911110122802</v>
+        <v>0.5633206135166107</v>
       </c>
       <c r="J20" t="n">
         <v>9.934704273616871</v>
@@ -1202,25 +1202,25 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.338141695074942</v>
+        <v>0.3390402260452667</v>
       </c>
       <c r="D21" t="n">
-        <v>10.72801545616561</v>
+        <v>14.96017573162526</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3376544610289568</v>
+        <v>0.3387919665955191</v>
       </c>
       <c r="F21" t="n">
         <v>14.96017573162526</v>
       </c>
       <c r="G21" t="n">
-        <v>0.33778894053319</v>
+        <v>0.562888430200662</v>
       </c>
       <c r="H21" t="n">
-        <v>14.96017573162526</v>
+        <v>10.72801545616561</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3381415874228698</v>
+        <v>0.5620548050224931</v>
       </c>
       <c r="J21" t="n">
         <v>10.72801545616561</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1155074168940402</v>
+        <v>0.08684372866799142</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1153311411952941</v>
+        <v>0.08684372866799142</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1153311411952941</v>
+        <v>0.08784742590101005</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1155074168940402</v>
+        <v>0.08751568927638456</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1200912455519105</v>
+        <v>0.09486148671525541</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1198775477976471</v>
+        <v>0.09486148671525541</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1198775477976471</v>
+        <v>0.09588870418461724</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1200906990137626</v>
+        <v>0.09572151724449862</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1246352230625761</v>
+        <v>0.1085877143407455</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1245978010070588</v>
+        <v>0.10858499184446</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1245978010070588</v>
+        <v>0.1085519560057937</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1246346765244283</v>
+        <v>0.1084300433152922</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.13511800378669</v>
+        <v>0.1235003897466319</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1348546850200699</v>
+        <v>0.1223863257882309</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1348546850200699</v>
+        <v>0.1159875739399114</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1349626750479327</v>
+        <v>0.1158203869997927</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1360233954614696</v>
+        <v>0.1236729590266319</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1348546850200699</v>
+        <v>0.1225588950682309</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1351580698570376</v>
+        <v>0.1159875739399114</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1360228489233218</v>
+        <v>0.1158203869997927</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1417,7 +1417,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.0147365431046726</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         <v>0.0147365431046726</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1464,19 +1464,19 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>0.0275334314020259</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1485,13 +1485,13 @@
         <v>0.0275334314020259</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1501,19 +1501,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.03882132685350974</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0.03882132685350974</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1538,19 +1538,19 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.04888731824920112</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>0.04888731824920112</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -1575,19 +1575,19 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.0579683588432312</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0.0579683588432312</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -1609,25 +1609,25 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0134704772311037</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01346070294870424</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01346069741362755</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0134704827661803</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>8.084742994771108</v>
@@ -1646,25 +1646,25 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01365237244499399</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0136432306275541</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01364323062755389</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01365236926784792</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>8.084742994771108</v>
@@ -1683,25 +1683,25 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01391188560502569</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01391171017403935</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01391171017403935</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01391188304290757</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>8.084742994771108</v>
@@ -1720,25 +1720,25 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01562508743624304</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01556527669537402</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01556527669537402</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01558958922182325</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>8.084742994771108</v>
@@ -1757,25 +1757,25 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0156331557591957</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01556527669537402</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01556527669537402</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>8.084742994771108</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01563303575742807</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>8.084742994771108</v>
@@ -1787,7 +1787,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -1797,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03553253809114845</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.135883270089286</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.135883270089286</v>
+        <v>0.09475343490972919</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03553253809114845</v>
+        <v>0.09475343490972919</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1834,145 +1834,145 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.06628992744512983</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.135883270089286</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.135883270089286</v>
+        <v>0.1767731398536796</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.06628992744512983</v>
+        <v>0.1767731398536796</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09334953007617701</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.135883270089286</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.135883270089286</v>
+        <v>0.2489320802031387</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09334953007617701</v>
+        <v>0.2489320802031387</v>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1174813095612829</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.135883270089286</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.135883270089286</v>
+        <v>0.3132834921634212</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1174813095612829</v>
+        <v>0.3132834921634212</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1392411358567997</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.135883270089286</v>
+        <v>3.029022053571428</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.135883270089286</v>
+        <v>0.3713096956181325</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1392411358567997</v>
+        <v>0.3713096956181325</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.06849645897088857</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.189654496557659</v>
+        <v>0.06849645897088857</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.127787811942419</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.189654496557659</v>
+        <v>0.127787811942419</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1799509013516665</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.189654496557659</v>
+        <v>0.1799509013516665</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2264699943350033</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.189654496557659</v>
+        <v>0.2264699943350033</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2684166474347946</v>
+        <v>2.189654496557659</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.189654496557659</v>
+        <v>0.2684166474347946</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0009475343490972921</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.0009475343490972921</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001767731398536796</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.001767731398536796</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.002489320802031387</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.002489320802031387</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.003132834921634212</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.003132834921634212</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.003713096956181325</v>
+        <v>0.03029022053571429</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.003713096956181325</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2352,34 +2352,34 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>0.5685206094583751</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>0.5685206094583751</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -2389,34 +2389,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>1.060638839122077</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>1.060638839122077</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2426,34 +2426,34 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>1.493592481218832</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>1.493592481218832</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -2463,34 +2463,34 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>1.879700952980527</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>1.879700952980527</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2500,34 +2500,34 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>18.17413232142857</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>2.227858173708795</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>2.227858173708795</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2558,13 +2558,13 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2595,13 +2595,13 @@
         <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2632,13 +2632,13 @@
         <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2669,13 +2669,13 @@
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2706,383 +2706,383 @@
         <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C62" t="n">
-        <v>0.05464918343696924</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05464918343696901</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.05464918343696901</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>0.05464918343696924</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4750877361504614</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6589062827811409</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.6579357244426037</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4915040778473956</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4750877361504614</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6619054793819794</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6609349210434423</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4915040778473956</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5273170196457403</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7146313707910997</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7136608124525626</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5437355155235537</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3472772489322486</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4709724444469278</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4387378055191104</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3472794031131279</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>4.470300525600001</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.04372641467501462</v>
       </c>
       <c r="D67" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>0.0439454948466237</v>
       </c>
       <c r="F67" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.03887414718686945</v>
       </c>
       <c r="H67" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>0.03887414718686946</v>
       </c>
       <c r="J67" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K67" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1.469068855226073</v>
       </c>
       <c r="D68" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1.458590116769465</v>
       </c>
       <c r="F68" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1.394730216334664</v>
       </c>
       <c r="H68" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1.392135226177283</v>
       </c>
       <c r="J68" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K68" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1.477251091744541</v>
       </c>
       <c r="D69" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1.458590116769465</v>
       </c>
       <c r="F69" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1.394730216334664</v>
       </c>
       <c r="H69" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1.392135226177283</v>
       </c>
       <c r="J69" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K69" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>3.881016711957625</v>
+        <v>1.487267572419368</v>
       </c>
       <c r="D70" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E70" t="n">
-        <v>3.881016711957625</v>
+        <v>1.473330021512364</v>
       </c>
       <c r="F70" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G70" t="n">
-        <v>3.881016711957625</v>
+        <v>1.39464835795004</v>
       </c>
       <c r="H70" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I70" t="n">
-        <v>3.881016711957625</v>
+        <v>1.395303048754716</v>
       </c>
       <c r="J70" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K70" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>3.881016711957625</v>
+        <v>1.416928320852819</v>
       </c>
       <c r="D71" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E71" t="n">
-        <v>3.881016711957625</v>
+        <v>1.421147228212451</v>
       </c>
       <c r="F71" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G71" t="n">
-        <v>3.881016711957625</v>
+        <v>1.361205492209161</v>
       </c>
       <c r="H71" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I71" t="n">
-        <v>3.881016711957625</v>
+        <v>1.361534708850942</v>
       </c>
       <c r="J71" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K71" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3092,34 +3092,34 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -3129,145 +3129,145 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K73" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>9.966425695852518</v>
       </c>
       <c r="D74" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>8.099245260484496</v>
       </c>
       <c r="F74" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>9.14097262192781</v>
       </c>
       <c r="H74" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>7.690899003696873</v>
       </c>
       <c r="J74" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K74" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>19.04851339633327</v>
       </c>
       <c r="D75" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>18.6719274425627</v>
       </c>
       <c r="F75" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>16.85763811886513</v>
       </c>
       <c r="H75" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>15.31990927300015</v>
       </c>
       <c r="J75" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K75" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>19.04851339633327</v>
       </c>
       <c r="D76" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>18.6719274425627</v>
       </c>
       <c r="F76" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>16.85763811886513</v>
       </c>
       <c r="H76" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>15.31990927300015</v>
       </c>
       <c r="J76" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K76" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -3277,34 +3277,34 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K77" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3314,34 +3314,34 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K78" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -3351,34 +3351,34 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K79" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3388,34 +3388,34 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K80" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -3425,34 +3425,34 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K81" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3462,367 +3462,367 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K82" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0008750366264110481</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0009043037442274315</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K83" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002144261466413958</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I84" t="n">
-        <v>0.002175764081691177</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K84" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C85" t="n">
-        <v>0.004370841141090771</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I85" t="n">
-        <v>0.004397954078027916</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K85" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C86" t="n">
-        <v>0.003495804514679738</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I86" t="n">
-        <v>0.003493650333800474</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K86" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.01281242651715367</v>
       </c>
       <c r="D87" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.01259334634554466</v>
       </c>
       <c r="F87" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.01766469400529885</v>
       </c>
       <c r="H87" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>0.01766469400529885</v>
       </c>
       <c r="J87" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K87" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.1044898565171536</v>
       </c>
       <c r="D88" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>0.1050604113803671</v>
       </c>
       <c r="F88" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.154095718464544</v>
       </c>
       <c r="H88" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>0.1571228378599275</v>
       </c>
       <c r="J88" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K88" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.1110346628643881</v>
       </c>
       <c r="D89" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>0.1104836363202387</v>
       </c>
       <c r="F89" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>0.1922019023480017</v>
       </c>
       <c r="H89" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>0.1952943309961741</v>
       </c>
       <c r="J89" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K89" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.1139384976667499</v>
       </c>
       <c r="D90" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>0.1094105674676955</v>
       </c>
       <c r="F90" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.1950044440909041</v>
       </c>
       <c r="H90" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>0.1958659896115666</v>
       </c>
       <c r="J90" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K90" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.1082176234203637</v>
       </c>
       <c r="D91" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>0.1047010714042362</v>
       </c>
       <c r="F91" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>0.1540688313520744</v>
       </c>
       <c r="H91" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>0.1540060792074076</v>
       </c>
       <c r="J91" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K91" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -3832,34 +3832,34 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K92" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -3869,34 +3869,34 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K93" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -3906,108 +3906,108 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K94" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1.914105276158364</v>
       </c>
       <c r="D95" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1.657245569812422</v>
       </c>
       <c r="F95" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2.579344425262511</v>
       </c>
       <c r="H95" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2.507519294999999</v>
       </c>
       <c r="J95" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K95" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1.914105276158364</v>
       </c>
       <c r="D96" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1.657245569812421</v>
       </c>
       <c r="F96" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2.579344425262511</v>
       </c>
       <c r="H96" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2.507519294999999</v>
       </c>
       <c r="J96" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K96" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -4017,34 +4017,34 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K97" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4054,34 +4054,34 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K98" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -4091,34 +4091,34 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K99" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4128,34 +4128,34 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K100" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -4165,34 +4165,34 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K101" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -4202,34 +4202,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K102" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -4239,34 +4239,34 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K103" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -4276,34 +4276,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K104" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -4313,34 +4313,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K105" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4350,34 +4350,34 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>4.470300525600001</v>
+        <v>70.382286072</v>
       </c>
       <c r="K106" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K107" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4424,34 +4424,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K108" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -4461,34 +4461,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K109" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4498,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K110" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4535,34 +4535,34 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>70.382286072</v>
+        <v>4.470300525600001</v>
       </c>
       <c r="K111" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4572,34 +4572,34 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -4609,34 +4609,34 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="E113" t="n">
-        <v>17.33655820369192</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="G113" t="n">
-        <v>17.38027421848903</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -4646,34 +4646,34 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="E114" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="G114" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -4683,34 +4683,34 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="E115" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="G115" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -4720,34 +4720,34 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="E116" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="G116" t="n">
-        <v>19.24846223603585</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>19.24846223603585</v>
+        <v>70.382286072</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>70.382286072</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -4757,182 +4757,182 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>146.14775294066</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>265.5568819273586</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>265.5568819273586</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>146.14775294066</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>16.53407425280264</v>
       </c>
       <c r="D118" t="n">
-        <v>195.9362286536411</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>16.5648940473197</v>
       </c>
       <c r="F118" t="n">
-        <v>265.5568819273586</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>265.5568819273586</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>195.9362286536411</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="D119" t="n">
-        <v>220.0614813359284</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="F119" t="n">
-        <v>265.5568819273586</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>265.5568819273586</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>220.0614813359284</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="D120" t="n">
-        <v>233.3262203850576</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="F120" t="n">
-        <v>265.5568819273586</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>265.5568819273586</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>233.3262203850576</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="D121" t="n">
-        <v>241.3250919862749</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>19.24846223603586</v>
       </c>
       <c r="F121" t="n">
-        <v>265.5568819273586</v>
+        <v>19.24846223603585</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>265.5568819273586</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>241.3250919862749</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -4942,34 +4942,34 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>6.98212132639982</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>12.89437269088045</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>12.89437269088045</v>
+        <v>146.14775294066</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>6.98212132639982</v>
+        <v>146.14775294066</v>
       </c>
       <c r="K122" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -4979,34 +4979,34 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>9.447276092768421</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>12.89437269088045</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>12.89437269088045</v>
+        <v>195.9362286536411</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>9.447276092768421</v>
+        <v>195.9362286536411</v>
       </c>
       <c r="K123" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -5016,34 +5016,34 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>10.64177905330155</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>12.89437269088045</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>12.89437269088045</v>
+        <v>220.0614813359284</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>10.64177905330155</v>
+        <v>220.0614813359284</v>
       </c>
       <c r="K124" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -5053,71 +5053,71 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>11.29855020813871</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>12.89437269088045</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>12.89437269088045</v>
+        <v>233.3262203850576</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>11.29855020813871</v>
+        <v>233.3262203850576</v>
       </c>
       <c r="K125" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>11.82267528667671</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>11.69459479819572</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>12.89437269088045</v>
+        <v>265.5568819273586</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>12.89437269088045</v>
+        <v>241.3250919862749</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>11.69459479819572</v>
+        <v>241.3250919862749</v>
       </c>
       <c r="K126" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,34 +5127,34 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.6060606060606061</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0.6060606060606061</v>
+        <v>6.98212132639982</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>6.98212132639982</v>
       </c>
       <c r="K127" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -5164,34 +5164,34 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.6060606060606061</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0.6060606060606061</v>
+        <v>9.447276092768421</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>9.447276092768421</v>
       </c>
       <c r="K128" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -5201,34 +5201,34 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6060606060606061</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6060606060606061</v>
+        <v>10.64177905330155</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>10.64177905330155</v>
       </c>
       <c r="K129" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -5238,34 +5238,34 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.6060606060606061</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6060606060606061</v>
+        <v>11.29855020813871</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>11.29855020813871</v>
       </c>
       <c r="K130" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -5275,34 +5275,34 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.6060606060606061</v>
+        <v>12.89437269088045</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6060606060606061</v>
+        <v>11.69459479819572</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>11.82267528667671</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>11.69459479819572</v>
       </c>
       <c r="K131" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,34 +5312,34 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -5349,34 +5349,34 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -5386,34 +5386,34 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -5423,34 +5423,34 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -5460,34 +5460,34 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>699.707770748064</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>699.707770748064</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -5497,34 +5497,34 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K137" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -5534,34 +5534,34 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K138" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -5571,34 +5571,34 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K139" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -5608,34 +5608,34 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K140" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -5645,589 +5645,589 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K141" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>31.06383992251658</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>187.674165119542</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E142" t="n">
-        <v>24.62918363103576</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G142" t="n">
-        <v>36.27727923968874</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I142" t="n">
-        <v>20.29473480258355</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>187.674165119542</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K142" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>56.22240699194667</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>278.4581379112628</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E143" t="n">
-        <v>52.86819216892452</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G143" t="n">
-        <v>61.2989596318371</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I143" t="n">
-        <v>48.53374334047231</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>278.4581379112628</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K143" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>107.9533645180444</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>339.2606853095913</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E144" t="n">
-        <v>105.7329678515848</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G144" t="n">
-        <v>111.5468086003072</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I144" t="n">
-        <v>102.3356183429869</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>339.2606853095913</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K144" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>121.6040887499884</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>382.129751166617</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E145" t="n">
-        <v>126.21491902212</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G145" t="n">
-        <v>121.7274815775719</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I145" t="n">
-        <v>124.6799277277981</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>382.129751166617</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K145" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>121.6040887499884</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>413.6172792906152</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E146" t="n">
-        <v>126.21491902212</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G146" t="n">
-        <v>121.7274815775719</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I146" t="n">
-        <v>124.6799277277981</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>413.6172792906152</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K146" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>1.28098332541133</v>
+        <v>29.05691950919376</v>
       </c>
       <c r="D147" t="n">
-        <v>7.798678686140327</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E147" t="n">
-        <v>1.304342804576988</v>
+        <v>38.02327143192299</v>
       </c>
       <c r="F147" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G147" t="n">
-        <v>1.280983325411331</v>
+        <v>23.71111015819446</v>
       </c>
       <c r="H147" t="n">
-        <v>31.0280691063521</v>
+        <v>187.674165119542</v>
       </c>
       <c r="I147" t="n">
-        <v>1.303259487680379</v>
+        <v>32.27363290261832</v>
       </c>
       <c r="J147" t="n">
-        <v>7.798678686140327</v>
+        <v>187.674165119542</v>
       </c>
       <c r="K147" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>4.795667130189207</v>
+        <v>43.74354031865509</v>
       </c>
       <c r="D148" t="n">
-        <v>11.91726841285981</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E148" t="n">
-        <v>4.814147516672517</v>
+        <v>51.4547619047619</v>
       </c>
       <c r="F148" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G148" t="n">
-        <v>4.814133475918659</v>
+        <v>37.14284895788511</v>
       </c>
       <c r="H148" t="n">
-        <v>31.0280691063521</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="I148" t="n">
-        <v>4.810659007768463</v>
+        <v>45.70512299273363</v>
       </c>
       <c r="J148" t="n">
-        <v>11.91726841285981</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="K148" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>6.148476580181235</v>
+        <v>108.8020341983704</v>
       </c>
       <c r="D149" t="n">
-        <v>14.67569304853479</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E149" t="n">
-        <v>6.326539067003607</v>
+        <v>116.041229982531</v>
       </c>
       <c r="F149" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G149" t="n">
-        <v>6.2044450282026</v>
+        <v>103.0358789290669</v>
       </c>
       <c r="H149" t="n">
-        <v>31.0280691063521</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="I149" t="n">
-        <v>6.291179300561396</v>
+        <v>110.2850443049958</v>
       </c>
       <c r="J149" t="n">
-        <v>14.67569304853479</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="K149" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>6.036269922327352</v>
+        <v>129.0440055896779</v>
       </c>
       <c r="D150" t="n">
-        <v>16.62053076386452</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E150" t="n">
-        <v>6.119546799796065</v>
+        <v>123.6697757391207</v>
       </c>
       <c r="F150" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G150" t="n">
-        <v>6.082396691514937</v>
+        <v>127.8922340166856</v>
       </c>
       <c r="H150" t="n">
-        <v>31.0280691063521</v>
+        <v>382.129751166617</v>
       </c>
       <c r="I150" t="n">
-        <v>6.045522070291846</v>
+        <v>121.2987921222713</v>
       </c>
       <c r="J150" t="n">
-        <v>16.62053076386452</v>
+        <v>382.129751166617</v>
       </c>
       <c r="K150" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>6.0370483974192</v>
+        <v>129.0440055896779</v>
       </c>
       <c r="D151" t="n">
-        <v>18.04902310522542</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E151" t="n">
-        <v>6.125708789907637</v>
+        <v>123.6697757391206</v>
       </c>
       <c r="F151" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G151" t="n">
-        <v>6.087908586621852</v>
+        <v>127.8922340166856</v>
       </c>
       <c r="H151" t="n">
-        <v>31.0280691063521</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="I151" t="n">
-        <v>6.050717096170695</v>
+        <v>121.2987921222713</v>
       </c>
       <c r="J151" t="n">
-        <v>18.04902310522542</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="K151" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1.280866453528425</v>
       </c>
       <c r="D152" t="n">
-        <v>187.674165119542</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1.255049690033419</v>
       </c>
       <c r="F152" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1.274642261452682</v>
       </c>
       <c r="H152" t="n">
-        <v>699.707770748064</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1.254789241850288</v>
       </c>
       <c r="J152" t="n">
-        <v>187.674165119542</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="K152" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>4.730263495084982</v>
       </c>
       <c r="D153" t="n">
-        <v>278.4581379112628</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>4.713915572904781</v>
       </c>
       <c r="F153" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4.706546150998783</v>
       </c>
       <c r="H153" t="n">
-        <v>699.707770748064</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>4.709827716700793</v>
       </c>
       <c r="J153" t="n">
-        <v>278.4581379112628</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="K153" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>6.200061995531626</v>
       </c>
       <c r="D154" t="n">
-        <v>339.2606853095913</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>6.116891826474207</v>
       </c>
       <c r="F154" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>6.126183948392011</v>
       </c>
       <c r="H154" t="n">
-        <v>699.707770748064</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>6.135534181575857</v>
       </c>
       <c r="J154" t="n">
-        <v>339.2606853095913</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="K154" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>6.153803232781596</v>
       </c>
       <c r="D155" t="n">
-        <v>382.129751166617</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>6.081685150833411</v>
       </c>
       <c r="F155" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>5.865532945470187</v>
       </c>
       <c r="H155" t="n">
-        <v>699.707770748064</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>5.792245317685518</v>
       </c>
       <c r="J155" t="n">
-        <v>382.129751166617</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="K155" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>6.151958462819434</v>
       </c>
       <c r="D156" t="n">
-        <v>413.6172792906152</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>6.082679553328745</v>
       </c>
       <c r="F156" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>5.883573080992734</v>
       </c>
       <c r="H156" t="n">
-        <v>699.707770748064</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>5.810962262795363</v>
       </c>
       <c r="J156" t="n">
-        <v>413.6172792906152</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="K156" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -6237,34 +6237,34 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>7.798678686140327</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>31.0280691063521</v>
+        <v>187.674165119542</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>7.798678686140327</v>
+        <v>187.674165119542</v>
       </c>
       <c r="K157" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
@@ -6274,34 +6274,34 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>11.91726841285981</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>31.0280691063521</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>11.91726841285981</v>
+        <v>278.4581379112628</v>
       </c>
       <c r="K158" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
@@ -6311,34 +6311,34 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>14.67569304853479</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>31.0280691063521</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>14.67569304853479</v>
+        <v>339.2606853095913</v>
       </c>
       <c r="K159" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
@@ -6348,34 +6348,34 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>16.62053076386452</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>31.0280691063521</v>
+        <v>382.129751166617</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>16.62053076386452</v>
+        <v>382.129751166617</v>
       </c>
       <c r="K160" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
@@ -6385,34 +6385,34 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>18.04902310522542</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>31.0280691063521</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>18.04902310522542</v>
+        <v>413.6172792906152</v>
       </c>
       <c r="K161" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -6422,34 +6422,34 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>699.707770748064</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>699.707770748064</v>
+        <v>7.798678686140327</v>
       </c>
       <c r="K162" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -6459,145 +6459,145 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>699.707770748064</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>699.707770748064</v>
+        <v>11.91726841285981</v>
       </c>
       <c r="K163" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>76.05297945735737</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E164" t="n">
-        <v>70.09486655141411</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G164" t="n">
-        <v>73.24991226070851</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>699.707770748064</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="I164" t="n">
-        <v>73.42470297873918</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>699.707770748064</v>
+        <v>14.67569304853479</v>
       </c>
       <c r="K164" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>90.52017707485672</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E165" t="n">
-        <v>79.7275369380185</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G165" t="n">
-        <v>84.6875929299607</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>699.707770748064</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="I165" t="n">
-        <v>87.54214883290159</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>699.707770748064</v>
+        <v>16.62053076386452</v>
       </c>
       <c r="K165" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>90.52017707485672</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E166" t="n">
-        <v>79.7275369380185</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G166" t="n">
-        <v>84.6875929299607</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>699.707770748064</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="I166" t="n">
-        <v>87.54214883290157</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>699.707770748064</v>
+        <v>18.04902310522542</v>
       </c>
       <c r="K166" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6607,182 +6607,182 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K167" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>0.08894748070658121</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E168" t="n">
-        <v>0.09132442895142252</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G168" t="n">
-        <v>0.092217225166217</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08726548408377678</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K168" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>2.33800578137556</v>
+        <v>34.90218496766156</v>
       </c>
       <c r="D169" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E169" t="n">
-        <v>2.234659444358468</v>
+        <v>34.85909297733102</v>
       </c>
       <c r="F169" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G169" t="n">
-        <v>2.341275525835196</v>
+        <v>34.94806509789232</v>
       </c>
       <c r="H169" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I169" t="n">
-        <v>2.193281115124412</v>
+        <v>34.87172660623067</v>
       </c>
       <c r="J169" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K169" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>3.450212439229441</v>
+        <v>49.91401698834612</v>
       </c>
       <c r="D170" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E170" t="n">
-        <v>3.44147348243352</v>
+        <v>53.4335851157561</v>
       </c>
       <c r="F170" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G170" t="n">
-        <v>3.462397539498288</v>
+        <v>50.85274861444051</v>
       </c>
       <c r="H170" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I170" t="n">
-        <v>3.440962750242947</v>
+        <v>56.02687450021256</v>
       </c>
       <c r="J170" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K170" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>3.456285337016892</v>
+        <v>49.91401698834612</v>
       </c>
       <c r="D171" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E171" t="n">
-        <v>3.441973743150347</v>
+        <v>53.4335851157561</v>
       </c>
       <c r="F171" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G171" t="n">
-        <v>3.463547895219771</v>
+        <v>50.85274861444051</v>
       </c>
       <c r="H171" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I171" t="n">
-        <v>3.442618722945707</v>
+        <v>56.02687450021256</v>
       </c>
       <c r="J171" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K171" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -6792,182 +6792,182 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K172" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>0.08288441026549501</v>
       </c>
       <c r="D173" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>0.08399167245759666</v>
       </c>
       <c r="F173" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>0.08323026754241972</v>
       </c>
       <c r="H173" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>0.08556096648559533</v>
       </c>
       <c r="J173" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K173" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>0.6501647278355615</v>
       </c>
       <c r="D174" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>0.7393199876722911</v>
       </c>
       <c r="F174" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>0.7117186574887249</v>
       </c>
       <c r="H174" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>0.7269780248162173</v>
       </c>
       <c r="J174" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K174" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>1.602212275680744</v>
       </c>
       <c r="D175" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1.667630014322919</v>
       </c>
       <c r="F175" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1.935520620110111</v>
       </c>
       <c r="H175" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>2.009284873824314</v>
       </c>
       <c r="J175" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K175" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>1.598216796336386</v>
       </c>
       <c r="D176" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>1.660795362521064</v>
       </c>
       <c r="F176" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1.919061439384789</v>
       </c>
       <c r="H176" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>1.995008932824906</v>
       </c>
       <c r="J176" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K176" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,34 +6977,34 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K177" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -7014,34 +7014,34 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K178" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -7051,34 +7051,34 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K179" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K180" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -7125,34 +7125,34 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K181" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>83.42697229498918</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>83.42697229498918</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K182" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>114.9301450330319</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>114.9301450330319</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K183" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>140.5979460799421</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>140.5979460799421</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K184" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>162.1111102622133</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>162.1111102622133</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K185" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,34 +7310,34 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>180.494690804983</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>180.494690804983</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K186" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -7347,34 +7347,34 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>3.069304059722748</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>3.069304059722748</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K187" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -7384,34 +7384,34 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>4.498506149122878</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>4.498506149122878</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K188" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -7421,34 +7421,34 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>5.662975365972627</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>5.662975365972627</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K189" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -7458,34 +7458,34 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>6.638961481865675</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>6.638961481865675</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K190" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,145 +7495,145 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>7.472968010060661</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>7.472968010060661</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K191" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>7.352217337365687</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>83.42697229498918</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E192" t="n">
-        <v>13.78687362884651</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G192" t="n">
-        <v>2.13877802019353</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I192" t="n">
-        <v>18.12132245729873</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>83.42697229498918</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K192" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>7.352217337365687</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>114.9301450330319</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E193" t="n">
-        <v>13.78687362884651</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G193" t="n">
-        <v>2.13877802019353</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I193" t="n">
-        <v>18.12132245729873</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>114.9301450330319</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K193" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>7.352217337365687</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>140.5979460799421</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E194" t="n">
-        <v>13.78687362884651</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G194" t="n">
-        <v>2.13877802019353</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I194" t="n">
-        <v>18.12132245729873</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>140.5979460799421</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K194" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -7643,34 +7643,34 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>162.1111102622133</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>162.1111102622133</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K195" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -7680,145 +7680,145 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>180.494690804983</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>699.707770748064</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>180.494690804983</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="K196" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>9.359137750688507</v>
       </c>
       <c r="D197" t="n">
-        <v>3.069304059722748</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0.3927858279592887</v>
       </c>
       <c r="F197" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>14.70494710168781</v>
       </c>
       <c r="H197" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I197" t="n">
-        <v>0.002024404848985258</v>
+        <v>6.142424357263941</v>
       </c>
       <c r="J197" t="n">
-        <v>3.069304059722748</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K197" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>9.359137750688507</v>
       </c>
       <c r="D198" t="n">
-        <v>4.498506149122878</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0.3927858279592887</v>
       </c>
       <c r="F198" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>14.70494710168781</v>
       </c>
       <c r="H198" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I198" t="n">
-        <v>0.002024404848985258</v>
+        <v>6.142424357263941</v>
       </c>
       <c r="J198" t="n">
-        <v>4.498506149122878</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K198" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>9.359137750688507</v>
       </c>
       <c r="D199" t="n">
-        <v>5.662975365972627</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0.3927858279592887</v>
       </c>
       <c r="F199" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>14.70494710168781</v>
       </c>
       <c r="H199" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I199" t="n">
-        <v>0.002024404848985258</v>
+        <v>6.142424357263941</v>
       </c>
       <c r="J199" t="n">
-        <v>5.662975365972627</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K199" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -7828,34 +7828,34 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>6.638961481865675</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>6.638961481865675</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K200" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7865,139 +7865,145 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>7.472968010060661</v>
+        <v>699.707770748064</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>31.0280691063521</v>
+        <v>699.707770748064</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>7.472968010060661</v>
+        <v>699.707770748064</v>
       </c>
       <c r="K201" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="D202" t="n">
-        <v>1.084828228313528</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="H202" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>1.084828228313528</v>
-      </c>
-      <c r="K202" t="inlineStr"/>
+        <v>31.0280691063521</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="D203" t="n">
-        <v>1.748391275895091</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="H203" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>1.748391275895091</v>
-      </c>
-      <c r="K203" t="inlineStr"/>
+        <v>31.0280691063521</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="D204" t="n">
-        <v>2.182785755513471</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="H204" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>2.182785755513471</v>
-      </c>
-      <c r="K204" t="inlineStr"/>
+        <v>31.0280691063521</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -8007,32 +8013,34 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>2.483031451106882</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>2.483031451106882</v>
-      </c>
-      <c r="K205" t="inlineStr"/>
+        <v>31.0280691063521</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8042,32 +8050,34 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>2.699949766579019</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>4</v>
+        <v>31.0280691063521</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>2.699949766579019</v>
-      </c>
-      <c r="K206" t="inlineStr"/>
+        <v>31.0280691063521</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -8077,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>1.084828228313528</v>
+        <v>4</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8089,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>4</v>
+        <v>1.084828228313528</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8102,7 +8112,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -8112,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>1.748391275895091</v>
+        <v>4</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -8124,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>4</v>
+        <v>1.748391275895091</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8137,7 +8147,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -8147,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>2.182785755513471</v>
+        <v>4</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -8159,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>4</v>
+        <v>2.182785755513471</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -8172,7 +8182,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8182,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>2.483031451106882</v>
+        <v>4</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -8194,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>4</v>
+        <v>2.483031451106882</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -8207,7 +8217,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8217,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>2.699949766579019</v>
+        <v>4</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -8229,7 +8239,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>4</v>
+        <v>2.699949766579019</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -8242,7 +8252,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8252,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>1.084828228313528</v>
+        <v>4</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -8264,7 +8274,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>4</v>
+        <v>1.084828228313528</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -8277,7 +8287,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8287,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>1.748391275895091</v>
+        <v>4</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -8299,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>4</v>
+        <v>1.748391275895091</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -8312,7 +8322,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8322,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>2.182785755513471</v>
+        <v>4</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -8334,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>4</v>
+        <v>2.182785755513471</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -8347,7 +8357,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8357,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>2.483031451106882</v>
+        <v>4</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -8369,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>4</v>
+        <v>2.483031451106882</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -8382,7 +8392,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8392,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>2.699949766579019</v>
+        <v>4</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -8404,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>4</v>
+        <v>2.699949766579019</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>
@@ -8413,6 +8423,181 @@
         <v>2.699949766579019</v>
       </c>
       <c r="K216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>4</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1.084828228313528</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1.084828228313528</v>
+      </c>
+      <c r="K217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>47849</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1.748391275895091</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1.748391275895091</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>49675</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2.182785755513471</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>2.182785755513471</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>51502</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2.483031451106882</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>2.483031451106882</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>53328</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2.699949766579019</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>2.699949766579019</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
